--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run2/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run2/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -808,772 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9829,0.0017,0.0062,0.0024</t>
-  </si>
-  <si>
-    <t>0.0013,0.0001,0.0001,0.9995</t>
-  </si>
-  <si>
-    <t>0.9575,0.0008,0.0002,0.0526</t>
-  </si>
-  <si>
-    <t>0.0191,0.0016,0.0004,0.9922</t>
-  </si>
-  <si>
-    <t>0.9950,0.0015,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9978,0.0004,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9976,0.0003,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9987,0.0000,0.0000,0.0008</t>
-  </si>
-  <si>
-    <t>0.9956,0.0008,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.9874,0.0043,0.0005,0.0021</t>
-  </si>
-  <si>
-    <t>0.9973,0.0013,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9465,0.0077,0.0517,0.0010</t>
-  </si>
-  <si>
-    <t>0.0605,0.0149,0.9236,0.0108</t>
-  </si>
-  <si>
-    <t>0.6445,0.0055,0.6122,0.0002</t>
-  </si>
-  <si>
-    <t>0.0042,0.0059,0.9850,0.0108</t>
-  </si>
-  <si>
-    <t>0.9631,0.0095,0.0200,0.0011</t>
-  </si>
-  <si>
-    <t>0.0004,0.9987,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.0028,0.9930,0.0074,0.0007</t>
-  </si>
-  <si>
-    <t>0.2589,0.8070,0.0068,0.0018</t>
-  </si>
-  <si>
-    <t>0.0054,0.9902,0.0061,0.0003</t>
-  </si>
-  <si>
-    <t>0.0007,0.9983,0.0037,0.0000</t>
-  </si>
-  <si>
-    <t>0.8280,0.0060,0.1472,0.0087</t>
-  </si>
-  <si>
-    <t>0.7575,0.0038,0.2116,0.0112</t>
-  </si>
-  <si>
-    <t>0.0010,0.0031,0.9943,0.0022</t>
-  </si>
-  <si>
-    <t>0.0333,0.0051,0.9713,0.0007</t>
-  </si>
-  <si>
-    <t>0.0228,0.0042,0.9697,0.0036</t>
-  </si>
-  <si>
-    <t>0.0338,0.0015,0.9704,0.0008</t>
-  </si>
-  <si>
-    <t>0.0008,0.0004,0.9956,0.0032</t>
-  </si>
-  <si>
-    <t>0.9742,0.0306,0.0045,0.0003</t>
-  </si>
-  <si>
-    <t>0.7693,0.1292,0.1401,0.0075</t>
-  </si>
-  <si>
-    <t>0.0091,0.0827,0.9617,0.0134</t>
-  </si>
-  <si>
-    <t>0.0429,0.3186,0.6208,0.0028</t>
-  </si>
-  <si>
-    <t>0.9432,0.0207,0.0065,0.0119</t>
-  </si>
-  <si>
-    <t>0.3947,0.0758,0.5925,0.0172</t>
-  </si>
-  <si>
-    <t>0.7133,0.3970,0.0070,0.0023</t>
-  </si>
-  <si>
-    <t>0.0236,0.9592,0.1216,0.0036</t>
-  </si>
-  <si>
-    <t>0.0273,0.5853,0.2903,0.1379</t>
-  </si>
-  <si>
-    <t>0.4733,0.0032,0.5761,0.0065</t>
-  </si>
-  <si>
-    <t>0.0282,0.0045,0.9696,0.0035</t>
-  </si>
-  <si>
-    <t>0.2137,0.0016,0.8688,0.0011</t>
-  </si>
-  <si>
-    <t>0.0251,0.0322,0.9742,0.0003</t>
-  </si>
-  <si>
-    <t>0.0010,0.9924,0.0029,0.0007</t>
-  </si>
-  <si>
-    <t>0.0277,0.0017,0.9677,0.0023</t>
-  </si>
-  <si>
-    <t>0.0027,0.6164,0.0006,0.8573</t>
-  </si>
-  <si>
-    <t>0.0029,0.9883,0.0023,0.0043</t>
-  </si>
-  <si>
-    <t>0.0206,0.9456,0.0177,0.0062</t>
-  </si>
-  <si>
-    <t>0.0003,0.9971,0.0018,0.0029</t>
-  </si>
-  <si>
-    <t>0.0003,0.0070,0.9979,0.0012</t>
-  </si>
-  <si>
-    <t>0.0127,0.0123,0.9743,0.0019</t>
-  </si>
-  <si>
-    <t>0.0611,0.0031,0.9564,0.0008</t>
-  </si>
-  <si>
-    <t>0.0456,0.0014,0.9708,0.0005</t>
-  </si>
-  <si>
-    <t>0.0041,0.0032,0.9943,0.0004</t>
-  </si>
-  <si>
-    <t>0.0118,0.0202,0.9735,0.0020</t>
-  </si>
-  <si>
-    <t>0.9894,0.0065,0.0009,0.0010</t>
-  </si>
-  <si>
-    <t>0.9863,0.0057,0.0035,0.0012</t>
-  </si>
-  <si>
-    <t>0.9898,0.0052,0.0018,0.0006</t>
-  </si>
-  <si>
-    <t>0.0160,0.0019,0.9801,0.0030</t>
-  </si>
-  <si>
-    <t>0.9952,0.0016,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9965,0.0007,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9924,0.0026,0.0006,0.0013</t>
-  </si>
-  <si>
-    <t>0.0016,0.6436,0.9885,0.0006</t>
-  </si>
-  <si>
-    <t>0.0014,0.0023,0.9960,0.0015</t>
-  </si>
-  <si>
-    <t>0.0016,0.0012,0.9906,0.0083</t>
-  </si>
-  <si>
-    <t>0.0010,0.8454,0.9848,0.0008</t>
-  </si>
-  <si>
-    <t>0.0007,0.0004,0.9968,0.0024</t>
-  </si>
-  <si>
-    <t>0.0012,0.9978,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0168,0.9875,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9798,0.0032,0.0184,0.0007</t>
-  </si>
-  <si>
-    <t>0.8356,0.1138,0.0743,0.0073</t>
-  </si>
-  <si>
-    <t>0.0032,0.0199,0.9906,0.0031</t>
-  </si>
-  <si>
-    <t>0.0017,0.9729,0.2894,0.0031</t>
-  </si>
-  <si>
-    <t>0.0080,0.5101,0.9139,0.0005</t>
-  </si>
-  <si>
-    <t>0.0024,0.9862,0.0452,0.0044</t>
-  </si>
-  <si>
-    <t>0.0094,0.9462,0.6023,0.0124</t>
-  </si>
-  <si>
-    <t>0.0010,0.0002,0.0099,0.9978</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.0001,0.9995</t>
-  </si>
-  <si>
-    <t>0.0088,0.0001,0.0004,0.9971</t>
-  </si>
-  <si>
-    <t>0.0028,0.0003,0.0004,0.9984</t>
-  </si>
-  <si>
-    <t>0.0016,0.0012,0.0026,0.9975</t>
-  </si>
-  <si>
-    <t>0.0005,0.0004,0.0002,0.9994</t>
-  </si>
-  <si>
-    <t>0.0152,0.8271,0.7988,0.0053</t>
-  </si>
-  <si>
-    <t>0.0152,0.4790,0.9263,0.0031</t>
-  </si>
-  <si>
-    <t>0.0242,0.5699,0.8093,0.0016</t>
-  </si>
-  <si>
-    <t>0.0012,0.9757,0.6050,0.0008</t>
-  </si>
-  <si>
-    <t>0.0010,0.9844,0.5729,0.0001</t>
-  </si>
-  <si>
-    <t>0.0031,0.9384,0.3771,0.0026</t>
-  </si>
-  <si>
-    <t>0.9974,0.0006,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9885,0.0036,0.0029,0.0013</t>
-  </si>
-  <si>
-    <t>0.9818,0.0148,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9979,0.0001,0.0000,0.0011</t>
-  </si>
-  <si>
-    <t>0.9955,0.0012,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9968,0.0004,0.0006,0.0006</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9869,0.0014,0.0057,0.0011</t>
+  </si>
+  <si>
+    <t>0.0205,0.0011,0.0005,0.9921</t>
+  </si>
+  <si>
+    <t>0.9243,0.0009,0.0021,0.1003</t>
+  </si>
+  <si>
+    <t>0.0524,0.0022,0.0005,0.9805</t>
+  </si>
+  <si>
+    <t>0.9973,0.0006,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9968,0.0008,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9966,0.0006,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.9979,0.0002,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9954,0.0012,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9963,0.0010,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.8115,0.0649,0.1383,0.0027</t>
+  </si>
+  <si>
+    <t>0.0051,0.0036,0.9860,0.0071</t>
+  </si>
+  <si>
+    <t>0.5523,0.0091,0.6447,0.0009</t>
+  </si>
+  <si>
+    <t>0.0088,0.0045,0.9862,0.0016</t>
+  </si>
+  <si>
+    <t>0.9915,0.0009,0.0055,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.9957,0.0022,0.0015</t>
+  </si>
+  <si>
+    <t>0.0046,0.9919,0.0071,0.0004</t>
+  </si>
+  <si>
+    <t>0.3950,0.6946,0.0106,0.0029</t>
+  </si>
+  <si>
+    <t>0.0005,0.9982,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.9978,0.0047,0.0000</t>
+  </si>
+  <si>
+    <t>0.8739,0.0023,0.1738,0.0014</t>
+  </si>
+  <si>
+    <t>0.2523,0.0284,0.7255,0.0251</t>
+  </si>
+  <si>
+    <t>0.0018,0.0004,0.9962,0.0006</t>
+  </si>
+  <si>
+    <t>0.0484,0.0028,0.9608,0.0006</t>
+  </si>
+  <si>
+    <t>0.0511,0.0005,0.9634,0.0018</t>
+  </si>
+  <si>
+    <t>0.0183,0.0022,0.9784,0.0010</t>
+  </si>
+  <si>
+    <t>0.0016,0.0004,0.9934,0.0023</t>
+  </si>
+  <si>
+    <t>0.6306,0.4687,0.0064,0.0011</t>
+  </si>
+  <si>
+    <t>0.6942,0.1982,0.1237,0.0201</t>
+  </si>
+  <si>
+    <t>0.0228,0.0578,0.9511,0.0143</t>
+  </si>
+  <si>
+    <t>0.0142,0.9562,0.0244,0.0053</t>
+  </si>
+  <si>
+    <t>0.9774,0.0053,0.0015,0.0056</t>
+  </si>
+  <si>
+    <t>0.9860,0.0049,0.0035,0.0009</t>
+  </si>
+  <si>
+    <t>0.1613,0.8864,0.0100,0.0018</t>
+  </si>
+  <si>
+    <t>0.0190,0.9693,0.0155,0.0077</t>
+  </si>
+  <si>
+    <t>0.0078,0.7614,0.2096,0.1131</t>
+  </si>
+  <si>
+    <t>0.7049,0.0028,0.4206,0.0032</t>
+  </si>
+  <si>
+    <t>0.0449,0.0948,0.9065,0.0091</t>
+  </si>
+  <si>
+    <t>0.3116,0.0055,0.7162,0.0078</t>
+  </si>
+  <si>
+    <t>0.0373,0.0584,0.9507,0.0020</t>
+  </si>
+  <si>
+    <t>0.0030,0.9765,0.0446,0.0011</t>
+  </si>
+  <si>
+    <t>0.0096,0.0081,0.9840,0.0012</t>
+  </si>
+  <si>
+    <t>0.1433,0.0264,0.0062,0.8838</t>
+  </si>
+  <si>
+    <t>0.0030,0.9855,0.0033,0.0038</t>
+  </si>
+  <si>
+    <t>0.0051,0.9815,0.0069,0.0041</t>
+  </si>
+  <si>
+    <t>0.0010,0.9932,0.0040,0.0019</t>
+  </si>
+  <si>
+    <t>0.0004,0.0068,0.9975,0.0014</t>
+  </si>
+  <si>
+    <t>0.0017,0.0569,0.9855,0.0037</t>
+  </si>
+  <si>
+    <t>0.0046,0.0010,0.9912,0.0013</t>
+  </si>
+  <si>
+    <t>0.0287,0.0006,0.9774,0.0007</t>
+  </si>
+  <si>
+    <t>0.0090,0.0027,0.9893,0.0003</t>
+  </si>
+  <si>
+    <t>0.0128,0.0057,0.9741,0.0023</t>
+  </si>
+  <si>
+    <t>0.9276,0.0936,0.0056,0.0009</t>
+  </si>
+  <si>
+    <t>0.9831,0.0057,0.0036,0.0035</t>
+  </si>
+  <si>
+    <t>0.9955,0.0007,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.0216,0.0031,0.9844,0.0011</t>
+  </si>
+  <si>
+    <t>0.9941,0.0011,0.0019,0.0007</t>
+  </si>
+  <si>
+    <t>0.9968,0.0008,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9952,0.0020,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.3686,0.9898,0.0005</t>
+  </si>
+  <si>
+    <t>0.0015,0.0029,0.9957,0.0012</t>
+  </si>
+  <si>
+    <t>0.0040,0.0386,0.9231,0.0394</t>
+  </si>
+  <si>
+    <t>0.0001,0.9358,0.9941,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0013,0.9935,0.0234</t>
+  </si>
+  <si>
+    <t>0.0043,0.9896,0.0031,0.0009</t>
+  </si>
+  <si>
+    <t>0.0141,0.9836,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9818,0.0019,0.0205,0.0005</t>
+  </si>
+  <si>
+    <t>0.3695,0.7154,0.0246,0.0037</t>
+  </si>
+  <si>
+    <t>0.0048,0.0188,0.9910,0.0014</t>
+  </si>
+  <si>
+    <t>0.0011,0.9761,0.7074,0.0003</t>
+  </si>
+  <si>
+    <t>0.0012,0.9600,0.6096,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9969,0.0965,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.9848,0.9347,0.0004</t>
+  </si>
+  <si>
+    <t>0.0037,0.0013,0.0361,0.9913</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.0002,0.9996</t>
+  </si>
+  <si>
+    <t>0.0033,0.0027,0.0001,0.9979</t>
+  </si>
+  <si>
+    <t>0.0074,0.0021,0.0051,0.9931</t>
+  </si>
+  <si>
+    <t>0.0035,0.0001,0.0007,0.9982</t>
+  </si>
+  <si>
+    <t>0.0002,0.0011,0.0003,0.9995</t>
+  </si>
+  <si>
+    <t>0.0045,0.9456,0.6396,0.0032</t>
+  </si>
+  <si>
+    <t>0.0021,0.7310,0.9781,0.0009</t>
+  </si>
+  <si>
+    <t>0.0134,0.8815,0.2283,0.0029</t>
+  </si>
+  <si>
+    <t>0.0015,0.5794,0.9820,0.0005</t>
+  </si>
+  <si>
+    <t>0.0003,0.9875,0.8690,0.0001</t>
+  </si>
+  <si>
+    <t>0.0059,0.5793,0.8897,0.0036</t>
+  </si>
+  <si>
+    <t>0.9972,0.0006,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9840,0.0194,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9855,0.0090,0.0022,0.0013</t>
+  </si>
+  <si>
+    <t>0.9953,0.0005,0.0003,0.0017</t>
+  </si>
+  <si>
+    <t>0.9897,0.0032,0.0002,0.0014</t>
+  </si>
+  <si>
+    <t>0.9973,0.0008,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9902,0.0031,0.0006,0.0018</t>
+  </si>
+  <si>
+    <t>0.9970,0.0011,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0004,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9970,0.0017,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9982,0.0003,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9941,0.0030,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9970,0.0004,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.0002,0.9958,0.0038</t>
+  </si>
+  <si>
+    <t>0.0200,0.0137,0.9558,0.0059</t>
+  </si>
+  <si>
+    <t>0.9802,0.0010,0.0085,0.0013</t>
+  </si>
+  <si>
+    <t>0.0039,0.0010,0.9928,0.0007</t>
+  </si>
+  <si>
+    <t>0.0205,0.9775,0.0107,0.0005</t>
+  </si>
+  <si>
+    <t>0.0056,0.9907,0.0127,0.0005</t>
+  </si>
+  <si>
+    <t>0.0256,0.9751,0.0098,0.0012</t>
+  </si>
+  <si>
+    <t>0.0121,0.9847,0.0052,0.0004</t>
+  </si>
+  <si>
+    <t>0.0026,0.9926,0.0194,0.0022</t>
+  </si>
+  <si>
+    <t>0.0076,0.9860,0.0145,0.0006</t>
+  </si>
+  <si>
+    <t>0.5978,0.4847,0.0009,0.0020</t>
+  </si>
+  <si>
+    <t>0.6904,0.0142,0.3912,0.0101</t>
+  </si>
+  <si>
+    <t>0.9711,0.0004,0.0425,0.0001</t>
+  </si>
+  <si>
+    <t>0.6772,0.0556,0.2624,0.0073</t>
+  </si>
+  <si>
+    <t>0.2481,0.0421,0.7185,0.0361</t>
+  </si>
+  <si>
+    <t>0.0150,0.0507,0.0249,0.9670</t>
+  </si>
+  <si>
+    <t>0.0215,0.9636,0.0244,0.0030</t>
+  </si>
+  <si>
+    <t>0.0002,0.9989,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0042,0.9780,0.0085,0.0316</t>
+  </si>
+  <si>
+    <t>0.0029,0.9777,0.6086,0.0004</t>
+  </si>
+  <si>
+    <t>0.0027,0.9924,0.0338,0.0004</t>
+  </si>
+  <si>
+    <t>0.8267,0.2787,0.0138,0.0016</t>
+  </si>
+  <si>
+    <t>0.8063,0.2108,0.0391,0.0016</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9951,0.0004,0.0009,0.0012</t>
+  </si>
+  <si>
+    <t>0.9937,0.0020,0.0017,0.0006</t>
+  </si>
+  <si>
+    <t>0.9868,0.0024,0.0044,0.0030</t>
+  </si>
+  <si>
+    <t>0.9958,0.0007,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9917,0.0017,0.0010,0.0019</t>
+  </si>
+  <si>
+    <t>0.9931,0.0023,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9976,0.0005,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.7851,0.9765,0.0004</t>
+  </si>
+  <si>
+    <t>0.0021,0.9373,0.8340,0.0009</t>
+  </si>
+  <si>
+    <t>0.0047,0.0115,0.9928,0.0003</t>
+  </si>
+  <si>
+    <t>0.0907,0.0281,0.8977,0.0055</t>
+  </si>
+  <si>
+    <t>0.9959,0.0003,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.9170,0.0056,0.0848,0.0033</t>
+  </si>
+  <si>
+    <t>0.0978,0.0017,0.9246,0.0032</t>
+  </si>
+  <si>
+    <t>0.9240,0.0081,0.0806,0.0023</t>
+  </si>
+  <si>
+    <t>0.3638,0.0001,0.0001,0.8967</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0009,0.9998</t>
+  </si>
+  <si>
+    <t>0.0040,0.0014,0.0009,0.9973</t>
+  </si>
+  <si>
+    <t>0.0092,0.0002,0.0020,0.9953</t>
+  </si>
+  <si>
+    <t>0.0066,0.7436,0.6089,0.0017</t>
+  </si>
+  <si>
+    <t>0.9978,0.0002,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.2367,0.7859,0.0023,0.0082</t>
+  </si>
+  <si>
+    <t>0.9972,0.0003,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.3862,0.7154,0.0048,0.0024</t>
+  </si>
+  <si>
+    <t>0.9721,0.0049,0.0034,0.0091</t>
+  </si>
+  <si>
+    <t>0.6205,0.0085,0.0055,0.4895</t>
+  </si>
+  <si>
+    <t>0.9897,0.0013,0.0053,0.0009</t>
+  </si>
+  <si>
+    <t>0.0011,0.0982,0.9920,0.0055</t>
+  </si>
+  <si>
+    <t>0.8999,0.0003,0.0002,0.1975</t>
+  </si>
+  <si>
+    <t>0.9663,0.0056,0.0033,0.0166</t>
+  </si>
+  <si>
+    <t>0.2421,0.6900,0.0894,0.0364</t>
+  </si>
+  <si>
+    <t>0.9604,0.0204,0.0099,0.0022</t>
+  </si>
+  <si>
+    <t>0.9688,0.0110,0.0186,0.0014</t>
+  </si>
+  <si>
+    <t>0.5784,0.4936,0.0104,0.0049</t>
+  </si>
+  <si>
+    <t>0.9437,0.0252,0.0319,0.0009</t>
+  </si>
+  <si>
+    <t>0.9885,0.0081,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.9979,0.0002,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9962,0.0011,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9945,0.0018,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9893,0.0004,0.0036,0.0026</t>
+  </si>
+  <si>
+    <t>0.9972,0.0003,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9611,0.0115,0.0047,0.0132</t>
+  </si>
+  <si>
+    <t>0.9958,0.0007,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9938,0.0007,0.0025,0.0009</t>
+  </si>
+  <si>
+    <t>0.8856,0.1405,0.0055,0.0036</t>
+  </si>
+  <si>
+    <t>0.8102,0.2068,0.0092,0.0047</t>
+  </si>
+  <si>
+    <t>0.6770,0.4485,0.0033,0.0009</t>
+  </si>
+  <si>
+    <t>0.8466,0.1239,0.0328,0.0095</t>
+  </si>
+  <si>
+    <t>0.9928,0.0040,0.0026,0.0001</t>
+  </si>
+  <si>
+    <t>0.9790,0.0157,0.0023,0.0007</t>
+  </si>
+  <si>
+    <t>0.9913,0.0029,0.0026,0.0014</t>
+  </si>
+  <si>
+    <t>0.9867,0.0105,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.0020,0.0175,0.9966,0.0005</t>
+  </si>
+  <si>
+    <t>0.9876,0.0060,0.0024,0.0007</t>
+  </si>
+  <si>
+    <t>0.0087,0.0012,0.9865,0.0010</t>
+  </si>
+  <si>
+    <t>0.0077,0.0048,0.9899,0.0007</t>
+  </si>
+  <si>
+    <t>0.0013,0.0016,0.9946,0.0052</t>
+  </si>
+  <si>
+    <t>0.0083,0.0029,0.9889,0.0006</t>
+  </si>
+  <si>
+    <t>0.0027,0.0021,0.9934,0.0017</t>
+  </si>
+  <si>
+    <t>0.0026,0.0005,0.9954,0.0004</t>
+  </si>
+  <si>
+    <t>0.0093,0.0012,0.9881,0.0013</t>
+  </si>
+  <si>
+    <t>0.0339,0.0081,0.9662,0.0029</t>
+  </si>
+  <si>
+    <t>0.0635,0.0039,0.9529,0.0006</t>
+  </si>
+  <si>
+    <t>0.0518,0.0059,0.9440,0.0055</t>
+  </si>
+  <si>
+    <t>0.2068,0.0304,0.7754,0.0028</t>
+  </si>
+  <si>
+    <t>0.1643,0.0552,0.8434,0.0048</t>
+  </si>
+  <si>
+    <t>0.6384,0.0064,0.4405,0.0036</t>
+  </si>
+  <si>
+    <t>0.1030,0.0162,0.9255,0.0045</t>
+  </si>
+  <si>
+    <t>0.2552,0.0273,0.7380,0.0281</t>
+  </si>
+  <si>
+    <t>0.0429,0.9422,0.0228,0.0045</t>
+  </si>
+  <si>
+    <t>0.1223,0.9249,0.0030,0.0007</t>
+  </si>
+  <si>
+    <t>0.9432,0.0640,0.0075,0.0011</t>
+  </si>
+  <si>
+    <t>0.8845,0.2151,0.0031,0.0006</t>
+  </si>
+  <si>
+    <t>0.2059,0.8647,0.0019,0.0008</t>
+  </si>
+  <si>
+    <t>0.7596,0.0517,0.1934,0.0196</t>
+  </si>
+  <si>
+    <t>0.9553,0.0009,0.0733,0.0002</t>
+  </si>
+  <si>
+    <t>0.9316,0.0037,0.0475,0.0068</t>
+  </si>
+  <si>
+    <t>0.8333,0.0310,0.1298,0.0110</t>
+  </si>
+  <si>
+    <t>0.7159,0.0005,0.3623,0.0013</t>
+  </si>
+  <si>
+    <t>0.0032,0.0103,0.9860,0.0095</t>
+  </si>
+  <si>
+    <t>0.0084,0.1430,0.8928,0.0270</t>
+  </si>
+  <si>
+    <t>0.0507,0.0113,0.9369,0.0058</t>
+  </si>
+  <si>
+    <t>0.0449,0.0128,0.9567,0.0016</t>
+  </si>
+  <si>
+    <t>0.0071,0.1110,0.9663,0.0014</t>
+  </si>
+  <si>
+    <t>0.9944,0.0011,0.0004,0.0017</t>
+  </si>
+  <si>
+    <t>0.9977,0.0005,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9910,0.0069,0.0012,0.0003</t>
   </si>
   <si>
     <t>0.9974,0.0008,0.0003,0.0002</t>
   </si>
   <si>
-    <t>0.9913,0.0047,0.0012,0.0007</t>
-  </si>
-  <si>
-    <t>0.9988,0.0000,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9935,0.0044,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9977,0.0003,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.0042,0.0008,0.9926,0.0014</t>
-  </si>
-  <si>
-    <t>0.0321,0.0165,0.9520,0.0043</t>
-  </si>
-  <si>
-    <t>0.9679,0.0007,0.0059,0.0071</t>
-  </si>
-  <si>
-    <t>0.0116,0.0007,0.9844,0.0014</t>
-  </si>
-  <si>
-    <t>0.0094,0.9823,0.0039,0.0039</t>
-  </si>
-  <si>
-    <t>0.0041,0.9901,0.0077,0.0026</t>
-  </si>
-  <si>
-    <t>0.0312,0.9687,0.0126,0.0005</t>
-  </si>
-  <si>
-    <t>0.0344,0.9609,0.0071,0.0028</t>
-  </si>
-  <si>
-    <t>0.0924,0.9128,0.0075,0.0012</t>
-  </si>
-  <si>
-    <t>0.0066,0.9857,0.0137,0.0023</t>
-  </si>
-  <si>
-    <t>0.1097,0.9232,0.0067,0.0018</t>
-  </si>
-  <si>
-    <t>0.1975,0.5475,0.2765,0.1722</t>
-  </si>
-  <si>
-    <t>0.1294,0.0011,0.9418,0.0003</t>
-  </si>
-  <si>
-    <t>0.8824,0.0449,0.0542,0.0012</t>
-  </si>
-  <si>
-    <t>0.6592,0.0586,0.3875,0.0180</t>
-  </si>
-  <si>
-    <t>0.0114,0.0595,0.0176,0.9697</t>
-  </si>
-  <si>
-    <t>0.0073,0.9871,0.0040,0.0008</t>
-  </si>
-  <si>
-    <t>0.0018,0.9932,0.0007,0.0023</t>
-  </si>
-  <si>
-    <t>0.0026,0.9725,0.0082,0.1052</t>
-  </si>
-  <si>
-    <t>0.0010,0.9859,0.8140,0.0004</t>
-  </si>
-  <si>
-    <t>0.0330,0.9622,0.0440,0.0003</t>
-  </si>
-  <si>
-    <t>0.6834,0.3836,0.0380,0.0017</t>
-  </si>
-  <si>
-    <t>0.8619,0.2273,0.0069,0.0005</t>
-  </si>
-  <si>
-    <t>0.9960,0.0005,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9944,0.0004,0.0003,0.0036</t>
-  </si>
-  <si>
-    <t>0.9972,0.0010,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9965,0.0001,0.0002,0.0021</t>
-  </si>
-  <si>
-    <t>0.9979,0.0001,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9960,0.0016,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9960,0.0008,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.9953,0.0003,0.0008,0.0017</t>
-  </si>
-  <si>
-    <t>0.0065,0.8408,0.8389,0.0022</t>
-  </si>
-  <si>
-    <t>0.0112,0.6249,0.8935,0.0030</t>
-  </si>
-  <si>
-    <t>0.0251,0.0210,0.9777,0.0004</t>
-  </si>
-  <si>
-    <t>0.1287,0.0368,0.8750,0.0029</t>
-  </si>
-  <si>
-    <t>0.9773,0.0015,0.0192,0.0008</t>
-  </si>
-  <si>
-    <t>0.7117,0.0098,0.3992,0.0010</t>
-  </si>
-  <si>
-    <t>0.3766,0.0007,0.6766,0.0032</t>
-  </si>
-  <si>
-    <t>0.9339,0.0102,0.0696,0.0015</t>
-  </si>
-  <si>
-    <t>0.0692,0.0003,0.0003,0.9855</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0589,0.9993</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.0028,0.9988</t>
-  </si>
-  <si>
-    <t>0.0030,0.0007,0.0013,0.9974</t>
-  </si>
-  <si>
-    <t>0.0055,0.5998,0.8646,0.0017</t>
-  </si>
-  <si>
-    <t>0.9945,0.0005,0.0023,0.0006</t>
-  </si>
-  <si>
-    <t>0.0346,0.9496,0.0008,0.0142</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.4076,0.7126,0.0078,0.0020</t>
-  </si>
-  <si>
-    <t>0.9934,0.0007,0.0010,0.0015</t>
-  </si>
-  <si>
-    <t>0.1611,0.0012,0.0112,0.9122</t>
-  </si>
-  <si>
-    <t>0.9924,0.0004,0.0017,0.0019</t>
-  </si>
-  <si>
-    <t>0.0009,0.0221,0.9955,0.0043</t>
-  </si>
-  <si>
-    <t>0.1961,0.0002,0.0016,0.9075</t>
-  </si>
-  <si>
-    <t>0.8269,0.0037,0.0012,0.2120</t>
-  </si>
-  <si>
-    <t>0.1219,0.8263,0.0613,0.0309</t>
-  </si>
-  <si>
-    <t>0.9956,0.0015,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9827,0.0091,0.0051,0.0010</t>
-  </si>
-  <si>
-    <t>0.5346,0.4956,0.0021,0.0052</t>
-  </si>
-  <si>
-    <t>0.6323,0.0225,0.5241,0.0013</t>
-  </si>
-  <si>
-    <t>0.9903,0.0035,0.0034,0.0002</t>
-  </si>
-  <si>
-    <t>0.9982,0.0001,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9967,0.0004,0.0007,0.0008</t>
-  </si>
-  <si>
-    <t>0.9918,0.0026,0.0031,0.0005</t>
-  </si>
-  <si>
-    <t>0.9917,0.0002,0.0016,0.0032</t>
-  </si>
-  <si>
-    <t>0.9952,0.0004,0.0004,0.0022</t>
-  </si>
-  <si>
-    <t>0.9850,0.0054,0.0032,0.0018</t>
-  </si>
-  <si>
-    <t>0.9937,0.0021,0.0012,0.0007</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9420,0.0782,0.0041,0.0007</t>
-  </si>
-  <si>
-    <t>0.7092,0.4459,0.0075,0.0008</t>
-  </si>
-  <si>
-    <t>0.7800,0.3184,0.0074,0.0016</t>
-  </si>
-  <si>
-    <t>0.8560,0.0313,0.1516,0.0068</t>
-  </si>
-  <si>
-    <t>0.9939,0.0032,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9922,0.0028,0.0028,0.0003</t>
-  </si>
-  <si>
-    <t>0.9914,0.0031,0.0037,0.0004</t>
-  </si>
-  <si>
-    <t>0.9937,0.0014,0.0017,0.0006</t>
-  </si>
-  <si>
-    <t>0.0039,0.0049,0.9954,0.0005</t>
-  </si>
-  <si>
-    <t>0.9862,0.0089,0.0021,0.0005</t>
-  </si>
-  <si>
-    <t>0.0011,0.0017,0.9969,0.0004</t>
-  </si>
-  <si>
-    <t>0.0058,0.0702,0.9843,0.0020</t>
-  </si>
-  <si>
-    <t>0.0005,0.0006,0.9976,0.0014</t>
-  </si>
-  <si>
-    <t>0.0153,0.0067,0.9753,0.0016</t>
-  </si>
-  <si>
-    <t>0.0033,0.0015,0.9962,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.0009,0.9981,0.0002</t>
-  </si>
-  <si>
-    <t>0.0041,0.0030,0.9931,0.0010</t>
-  </si>
-  <si>
-    <t>0.0837,0.0117,0.9127,0.0127</t>
-  </si>
-  <si>
-    <t>0.6011,0.0083,0.5149,0.0050</t>
-  </si>
-  <si>
-    <t>0.1225,0.0137,0.8793,0.0097</t>
-  </si>
-  <si>
-    <t>0.5309,0.0218,0.5873,0.0011</t>
-  </si>
-  <si>
-    <t>0.4065,0.5538,0.0461,0.0263</t>
-  </si>
-  <si>
-    <t>0.1168,0.0251,0.8765,0.0052</t>
-  </si>
-  <si>
-    <t>0.8360,0.0029,0.2581,0.0017</t>
-  </si>
-  <si>
-    <t>0.3577,0.0137,0.7482,0.0060</t>
-  </si>
-  <si>
-    <t>0.1161,0.8863,0.0464,0.0010</t>
-  </si>
-  <si>
-    <t>0.1812,0.8635,0.0016,0.0017</t>
-  </si>
-  <si>
-    <t>0.8795,0.1981,0.0043,0.0005</t>
-  </si>
-  <si>
-    <t>0.9786,0.0270,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.8569,0.2206,0.0057,0.0018</t>
-  </si>
-  <si>
-    <t>0.6674,0.1973,0.0760,0.0140</t>
-  </si>
-  <si>
-    <t>0.9009,0.0292,0.0716,0.0020</t>
-  </si>
-  <si>
-    <t>0.8602,0.0117,0.0987,0.0162</t>
-  </si>
-  <si>
-    <t>0.4560,0.0106,0.6880,0.0071</t>
-  </si>
-  <si>
-    <t>0.7755,0.0023,0.2758,0.0029</t>
-  </si>
-  <si>
-    <t>0.0132,0.0070,0.9713,0.0079</t>
-  </si>
-  <si>
-    <t>0.0628,0.1249,0.9013,0.0038</t>
-  </si>
-  <si>
-    <t>0.3605,0.0233,0.6790,0.0016</t>
-  </si>
-  <si>
-    <t>0.1468,0.0045,0.9173,0.0014</t>
-  </si>
-  <si>
-    <t>0.0031,0.0667,0.9701,0.0034</t>
-  </si>
-  <si>
-    <t>0.9968,0.0011,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9956,0.0011,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.9935,0.0011,0.0001,0.0015</t>
-  </si>
-  <si>
-    <t>0.9977,0.0012,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9923,0.0059,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9958,0.0021,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0002,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9952,0.0004,0.0004,0.0024</t>
-  </si>
-  <si>
-    <t>0.0004,0.0004,0.9983,0.0014</t>
-  </si>
-  <si>
-    <t>0.0732,0.0356,0.9002,0.0255</t>
-  </si>
-  <si>
-    <t>0.9441,0.0049,0.0495,0.0036</t>
-  </si>
-  <si>
-    <t>0.0068,0.0011,0.9910,0.0005</t>
-  </si>
-  <si>
-    <t>0.0011,0.0007,0.9946,0.0033</t>
-  </si>
-  <si>
-    <t>0.0089,0.0225,0.9785,0.0019</t>
-  </si>
-  <si>
-    <t>0.0080,0.0159,0.9843,0.0047</t>
-  </si>
-  <si>
-    <t>0.0116,0.0071,0.9719,0.0074</t>
-  </si>
-  <si>
-    <t>0.0160,0.0042,0.9848,0.0007</t>
-  </si>
-  <si>
-    <t>0.0012,0.0010,0.9957,0.0023</t>
-  </si>
-  <si>
-    <t>0.0240,0.0384,0.9589,0.0056</t>
-  </si>
-  <si>
-    <t>0.7668,0.0004,0.4379,0.0004</t>
-  </si>
-  <si>
-    <t>0.9208,0.0027,0.1016,0.0017</t>
-  </si>
-  <si>
-    <t>0.9235,0.0038,0.0696,0.0029</t>
-  </si>
-  <si>
-    <t>0.9837,0.0074,0.0005,0.0020</t>
-  </si>
-  <si>
-    <t>0.9937,0.0028,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9976,0.0006,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9947,0.0020,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.9963,0.0005,0.0003,0.0013</t>
-  </si>
-  <si>
-    <t>0.9966,0.0019,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9944,0.0016,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0130,0.0009,0.9910,0.0001</t>
-  </si>
-  <si>
-    <t>0.0061,0.0030,0.9936,0.0001</t>
-  </si>
-  <si>
-    <t>0.0096,0.0067,0.9826,0.0016</t>
-  </si>
-  <si>
-    <t>0.0505,0.0347,0.9132,0.0049</t>
-  </si>
-  <si>
-    <t>0.0020,0.0027,0.9946,0.0007</t>
-  </si>
-  <si>
-    <t>0.0967,0.0031,0.9143,0.0021</t>
-  </si>
-  <si>
-    <t>0.0323,0.0030,0.9702,0.0035</t>
-  </si>
-  <si>
-    <t>0.7133,0.0088,0.4004,0.0026</t>
-  </si>
-  <si>
-    <t>0.7636,0.0001,0.0060,0.1194</t>
-  </si>
-  <si>
-    <t>0.0132,0.0236,0.0066,0.9837</t>
-  </si>
-  <si>
-    <t>0.0122,0.0008,0.0005,0.9952</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0006,0.9995</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.0016,0.9993</t>
-  </si>
-  <si>
-    <t>0.8114,0.0080,0.0105,0.2236</t>
+    <t>0.9951,0.0007,0.0002,0.0017</t>
+  </si>
+  <si>
+    <t>0.9975,0.0006,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9947,0.0035,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0001,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.0035,0.0015,0.9937,0.0018</t>
+  </si>
+  <si>
+    <t>0.1149,0.0588,0.8523,0.0236</t>
+  </si>
+  <si>
+    <t>0.8873,0.0059,0.1161,0.0069</t>
+  </si>
+  <si>
+    <t>0.0033,0.0024,0.9937,0.0012</t>
+  </si>
+  <si>
+    <t>0.0022,0.0038,0.9959,0.0003</t>
+  </si>
+  <si>
+    <t>0.0120,0.0722,0.9635,0.0021</t>
+  </si>
+  <si>
+    <t>0.0038,0.0010,0.9929,0.0019</t>
+  </si>
+  <si>
+    <t>0.0097,0.0021,0.9869,0.0014</t>
+  </si>
+  <si>
+    <t>0.0036,0.0005,0.9944,0.0005</t>
+  </si>
+  <si>
+    <t>0.0073,0.0016,0.9872,0.0022</t>
+  </si>
+  <si>
+    <t>0.0497,0.0230,0.9374,0.0069</t>
+  </si>
+  <si>
+    <t>0.9566,0.0015,0.0652,0.0006</t>
+  </si>
+  <si>
+    <t>0.5626,0.0031,0.5979,0.0013</t>
+  </si>
+  <si>
+    <t>0.9933,0.0001,0.0136,0.0000</t>
+  </si>
+  <si>
+    <t>0.9968,0.0008,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9918,0.0040,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.9968,0.0014,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9896,0.0033,0.0032,0.0014</t>
+  </si>
+  <si>
+    <t>0.9935,0.0003,0.0001,0.0060</t>
+  </si>
+  <si>
+    <t>0.9933,0.0039,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.9965,0.0012,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9970,0.0003,0.0000,0.0012</t>
+  </si>
+  <si>
+    <t>0.0821,0.0149,0.9183,0.0011</t>
+  </si>
+  <si>
+    <t>0.0017,0.0028,0.9966,0.0002</t>
+  </si>
+  <si>
+    <t>0.0524,0.2834,0.9032,0.0121</t>
+  </si>
+  <si>
+    <t>0.0233,0.0466,0.9256,0.0075</t>
+  </si>
+  <si>
+    <t>0.0029,0.0008,0.9935,0.0009</t>
+  </si>
+  <si>
+    <t>0.0046,0.0007,0.9931,0.0006</t>
+  </si>
+  <si>
+    <t>0.2174,0.0107,0.8072,0.0142</t>
+  </si>
+  <si>
+    <t>0.0608,0.0086,0.9237,0.0052</t>
+  </si>
+  <si>
+    <t>0.8504,0.0008,0.0167,0.0669</t>
+  </si>
+  <si>
+    <t>0.0988,0.0073,0.0057,0.9481</t>
+  </si>
+  <si>
+    <t>0.0206,0.0002,0.0005,0.9932</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.0028,0.9987</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.0004,0.9998</t>
+  </si>
+  <si>
+    <t>0.9485,0.0038,0.0220,0.0102</t>
   </si>
 </sst>
 </file>
@@ -2152,7 +2152,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
         <v>279</v>
@@ -2278,7 +2278,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>288</v>
@@ -2404,7 +2404,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>297</v>
@@ -2432,7 +2432,7 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
         <v>299</v>
@@ -2446,7 +2446,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
         <v>300</v>
@@ -2488,7 +2488,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D40" t="s">
         <v>303</v>
@@ -2572,7 +2572,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>309</v>
@@ -2810,7 +2810,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
         <v>326</v>
@@ -2922,7 +2922,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D71" t="s">
         <v>334</v>
@@ -2950,7 +2950,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>336</v>
@@ -3104,7 +3104,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>347</v>
@@ -3118,7 +3118,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
         <v>348</v>
@@ -3160,7 +3160,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>351</v>
@@ -3538,7 +3538,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
         <v>378</v>
@@ -3552,7 +3552,7 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
         <v>379</v>
@@ -3566,7 +3566,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
         <v>380</v>
@@ -3594,7 +3594,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>382</v>
@@ -4084,7 +4084,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
         <v>417</v>
@@ -4126,7 +4126,7 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D157" t="s">
         <v>420</v>
@@ -4210,7 +4210,7 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
         <v>426</v>
@@ -4644,7 +4644,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>457</v>
@@ -4658,7 +4658,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
         <v>458</v>
@@ -4672,7 +4672,7 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
         <v>459</v>
@@ -4756,7 +4756,7 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
         <v>465</v>
@@ -4812,7 +4812,7 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
         <v>469</v>
@@ -5190,7 +5190,7 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D233" t="s">
         <v>496</v>
@@ -5428,7 +5428,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>513</v>
